--- a/docs/Đăng ký đề tài ĐATN-Lê Hà Bình.xlsx
+++ b/docs/Đăng ký đề tài ĐATN-Lê Hà Bình.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\hoc tap\DO-AN-TOT-NGHIEP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED6FB0E-70CB-4136-9F08-AB44A5D3C9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A07392-DFE7-4219-9827-D50ABFA18C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2116B685-F135-47D6-B1D5-9A2A2D157225}"/>
   </bookViews>
@@ -98,7 +98,8 @@
     <t>PostgreSQL</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Xem bài viết dăng bài viết, sự kiện
+    <t xml:space="preserve"> - Quản lý người dùng (phân quyền, duyệt bài)
+ - Xem bài viết dăng bài viết, sự kiện
  - Nhắn tin, tạo cuộc gọi
  - Xem số điểm, phần điểm sẽ tự động tổng kết và đánh giá xem là sinh viên có khả năng được học bổng hay không ?
  - Đăng bài kèm sự kiên cho phép sinh viên đăng ký tham gia
